--- a/artfynd/A 45485-2023 artfynd.xlsx
+++ b/artfynd/A 45485-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>116967814</v>
       </c>
       <c r="B2" t="n">
-        <v>57256</v>
+        <v>57257</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 45485-2023 artfynd.xlsx
+++ b/artfynd/A 45485-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125789477</v>
       </c>
       <c r="B3" t="n">
-        <v>57562</v>
+        <v>57563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45485-2023 artfynd.xlsx
+++ b/artfynd/A 45485-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -916,6 +916,125 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126280870</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57602</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102110</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fjällvråk</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Buteo lagopus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Renslakteriet, Fyrås, Hammerdal, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>516005</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7044356</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>06:16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>06:16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Joakim Danielsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45485-2023 artfynd.xlsx
+++ b/artfynd/A 45485-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125789477</v>
       </c>
       <c r="B3" t="n">
-        <v>57563</v>
+        <v>57567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>126280870</v>
       </c>
       <c r="B4" t="n">
-        <v>57602</v>
+        <v>57606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45485-2023 artfynd.xlsx
+++ b/artfynd/A 45485-2023 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>125789477</v>
       </c>
       <c r="B3" t="n">
-        <v>57567</v>
+        <v>57568</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
         <v>126280870</v>
       </c>
       <c r="B4" t="n">
-        <v>57606</v>
+        <v>57607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
